--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:58</t>
+    <t xml:space="preserve">2026-09-10 01:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:10</t>
+    <t xml:space="preserve">2026-09-12 22:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:22</t>
+    <t xml:space="preserve">2026-09-23 23:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:51</t>
+    <t xml:space="preserve">2026-10-02 16:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Tirúa</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Concepción</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:20</t>
+    <t xml:space="preserve">2026-10-04 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:31</t>
+    <t xml:space="preserve">2026-10-05 16:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
